--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260715.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260715.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>155,085</t>
+          <t>154,135</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>28.02%</t>
+          <t>28.55%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>17,615</t>
+          <t>17,515</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8.73%</t>
+          <t>8.68%</t>
         </is>
       </c>
     </row>
@@ -655,100 +655,100 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>112,600</t>
+          <t>111,600</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6.70%</t>
+          <t>6.95%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>MRVL US</t>
+          <t>NEE US</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Marvell Technology Inc</t>
+          <t>NextEra Energy Inc</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>57,195</t>
+          <t>136,015</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.91%</t>
+          <t>5.69%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>NEE US</t>
+          <t>MRVL US</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>NextEra Energy Inc</t>
+          <t>Marvell Technology Inc</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>136,965</t>
+          <t>56,815</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.70%</t>
+          <t>5.51%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>SO US</t>
+          <t>NOW US</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>南方公司</t>
+          <t>ServiceNow Inc</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>73,945</t>
+          <t>66,670</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.30%</t>
+          <t>3.28%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>NOW US</t>
+          <t>SO US</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>ServiceNow Inc</t>
+          <t>南方公司</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>67,270</t>
+          <t>73,545</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.28%</t>
+          <t>3.27%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.06%</t>
+          <t>3.09%</t>
         </is>
       </c>
     </row>
@@ -787,56 +787,56 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>51,055</t>
+          <t>50,735</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>2.96%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>NET US</t>
+          <t>CEG US</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Cloudflare公司</t>
+          <t>星座能源公司</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>20,583</t>
+          <t>22,125</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.70%</t>
+          <t>2.68%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>CEG US</t>
+          <t>NET US</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>星座能源公司</t>
+          <t>Cloudflare公司</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>22,255</t>
+          <t>20,483</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.65%</t>
+          <t>2.63%</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>35,560</t>
+          <t>35,320</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.23%</t>
+          <t>2.20%</t>
         </is>
       </c>
     </row>
@@ -875,12 +875,12 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>86,815</t>
+          <t>86,215</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>1.92%</t>
         </is>
       </c>
     </row>
@@ -897,7 +897,7 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>57,575</t>
+          <t>57,185</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -919,12 +919,12 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>22,795</t>
+          <t>22,695</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.83%</t>
+          <t>1.88%</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>21,970</t>
+          <t>21,820</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>1.64%</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>29,928</t>
+          <t>29,728</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.61%</t>
+          <t>1.60%</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>40,800</t>
+          <t>40,530</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.51%</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>8,990</t>
+          <t>8,890</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>1.46%</t>
         </is>
       </c>
     </row>
@@ -1029,56 +1029,56 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>67,008</t>
+          <t>66,558</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.43%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>C_USD</t>
+          <t>ED US</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>聯合愛迪生</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>2,778,393</t>
+          <t>23,938</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.24%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>ED US</t>
+          <t>NBIS US</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>聯合愛迪生</t>
+          <t>尼比厄斯集團公眾有限公司</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>24,058</t>
+          <t>13,051</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>1.22%</t>
         </is>
       </c>
     </row>
@@ -1095,34 +1095,34 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>83,859,265</t>
+          <t>80,721,908</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>1.18%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>NBIS US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>尼比厄斯集團公眾有限公司</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>13,151</t>
+          <t>142,055</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>1.17%</t>
         </is>
       </c>
     </row>
@@ -1144,29 +1144,29 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.15%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>C_USD</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>143,015</t>
+          <t>2,350,575</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.16%</t>
+          <t>1.10%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>20,735</t>
+          <t>20,635</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.10%</t>
         </is>
       </c>
     </row>
@@ -1205,29 +1205,29 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>17,901</t>
+          <t>17,781</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.93%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>NRG US</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Centerpoint能源</t>
+          <t>NRG Energy Inc</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>42,230</t>
+          <t>13,205</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1239,22 +1239,22 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>NRG US</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>NRG Energy Inc</t>
+          <t>Centerpoint能源</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>13,305</t>
+          <t>42,130</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.85%</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>48,600</t>
+          <t>48,400</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.81%</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1293,12 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>22,087</t>
+          <t>21,937</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.79%</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>64,341,000</t>
+          <t>80,485,500</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>557,967</t>
+          <t>1,316,146</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
